--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL/a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL/a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Profundizacion.xlsx
@@ -9,9 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="URELINTER" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Por tipo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Facultad de Ingeniería" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convenios vigentes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convenio IGAC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Convenios vigentes'!$A$4:$I$9</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -575,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -698,7 +701,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>Que mencionan a la Facultad de Ingeniería</t>
+          <t>Aplican a la MCIC</t>
         </is>
       </c>
     </row>
@@ -713,29 +716,43 @@
         <v>167</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>El listado de URELINTER es institucional (toda la Universidad) y no se puede filtrar por programa. Fuente: https://urelinter.udistrital.edu.co/convenios/cooperacion-redes-asociaciones · descargado el 18/09/2026. Descrito por URELINTER como 'el listado de los convenios vigentes al último trimestre 2025'. Para copia de un convenio o información adicional: convenios-ceri@udistrital.edu.co.</t>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Complementan a la MCIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>El listado de URELINTER es institucional (toda la Universidad) y no se puede filtrar por programa. Fuente: https://urelinter.udistrital.edu.co/convenios/cooperacion-redes-asociaciones · descargado el 02/10/2026. Descrito por URELINTER como 'el listado de los convenios vigentes al último trimestre 2025'. Para copia de un convenio o información adicional: convenios-ceri@udistrital.edu.co.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="E12:F12"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="G12:H12"/>
+    <mergeCell ref="A15:B15"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A16:B16"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="G13:H13"/>
     <mergeCell ref="C7:H7"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C10:F10"/>
@@ -858,64 +875,76 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="90" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Convenios institucionales que mencionan a la Facultad de Ingeniería</t>
+          <t>Convenios que aplican o complementan a la MCIC</t>
         </is>
       </c>
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Búsqueda por texto sobre institución, denominación y objeto de cada convenio.</t>
+          <t>De los 388 convenios vigentes de URELINTER (descargado el 02/10/2026).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="13" t="inlineStr">
         <is>
+          <t>Relación</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>Nivel</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
-        <is>
-          <t>País</t>
-        </is>
-      </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
+          <t>País / categoría</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
           <t>Institución</t>
         </is>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="F4" s="13" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F4" s="13" t="inlineStr">
-        <is>
-          <t>Vigencia</t>
-        </is>
-      </c>
       <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Denominación</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>Vigencia hasta</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Objeto</t>
         </is>
@@ -924,35 +953,45 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
+          <t>Aplica a la MCIC</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
           <t>C-2012-12</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Estados Unidos</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Comisión Interamericana de Telecomunicaciones de la OEA- CITEL</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Convenio Marco</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Vigencia indefinida</t>
-        </is>
-      </c>
       <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Cooperación</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>N/A (Vigencia indefinida)</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Organización de seminarios, reuniones y mesas redondas sobre materias de interés común; colaboración en proyectos conjuntos, capacitación y publicaciones conjuntas entre otras.</t>
         </is>
@@ -961,229 +1000,348 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>C-2012-36</t>
+          <t>Aplica a la MCIC</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>C-2019-28</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Colombia IES</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Universidad de Caldas</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
+          <t>Universidad de Valparaiso</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
           <t>Convenio Específico</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
-        <is>
-          <t>Renovación Automática</t>
-        </is>
-      </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Establecer las bases para la movilidad académica de estudiantes de pregrado de Ingeniería de Sistemas de la UDFJC y de la Universidad de Caldas.</t>
+          <t>Movilidad de estudiantes</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>2027-06-26 (Renovación Automática)</t>
+        </is>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Convenio de Intercambio y/o movilidad estudiantil Objeto: Establecer un programa de intercambio estudiantil, en el podrán participar todos los estudiantes de la UDFJC y los estudiantes de la Escuela de Ingeniería Civil Industrial de la Facultad de Ingeniería de la Universidad de Valparaíso, el cual será regulado en el presente convenio.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>C-2016-10</t>
+          <t>Aplica a la MCIC</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>C-2022-29</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Colombia Otros Organismos</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>New Net S.A.</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
+          <t>Universidad Popular Autónoma del Estado de Puebla UPAEP</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
           <t>Convenio Específico</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Renovación Automática</t>
-        </is>
-      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Establecer términos de cooperación interinstitucional con el fin de optimizar la utilización de los recursos humanos tecnológicos y materiales de ambas entidades, por medio de Pasantías de los estudiantes de la UNIVERSIDAD (UDFJC) del Proyecto Curricular de Ingeniería de Sistemas en NEWNET S.A.</t>
+          <t>Movilidad estudianestes Facultad de Ingeniería</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>2027-08-17 (Vigente)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Convenio Específico de Movilidad Académica de Estudiantes y Docentes Objeto: El presente convenio tiene por objeto establecer las bases para la movilidad académica de estudiantes (pregrado y postgrado) de la facultad de ingeniería y de personal docente de la facultad de ingeniería de la “UDFJC” y de “UPAEP, A.C.”, en desarrollo del Convenio Marco de Cooperación celebrado entre “UPAEP, A.C.” y la “UDFJC”.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>C-2019-28</t>
+          <t>Complementa a la MCIC</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>C-2023-19</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Universidad de Valparaiso</t>
+          <t>Colombia IES</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
+          <t>Fundación UNIR</t>
+        </is>
+      </c>
+      <c r="F8" s="14" t="inlineStr">
+        <is>
           <t>Convenio Específico</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Renovación Automática</t>
-        </is>
-      </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Convenio de Intercambio y/o movilidad estudiantil Objeto: Establecer un programa de intercambio estudiantil, en el podrán participar todos los estudiantes de la UDFJC y los estudiantes de la Escuela de Ingeniería Civil Industrial de la Facultad de Ingeniería de la Universidad de Valparaíso, el cual será regulado en el presente convenio.</t>
+          <t>Cotitulación</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
+        <is>
+          <t>2030-06-28 (Vigente)</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>El objeto de este convenio consiste en regular la cooperación entre la UDFJC y la FUNDACIÓN para permitir el desarrollo del programa académico conjunto “Pregrado en Ingeniería de Software”, que se impartirá en modalidad virtual, previa obtención por la UDFJC del registro calificado adscrito a la Facultad de Ingeniería otorgado por el Ministerio de Educación Nacional (MEN), bajo los mecanismos y estrategias para el desarrollo conjunto de los procesos de diseño y gestión de las actividades académicas del programa que se desarrollan en el presente instrumento.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>C-2022-29</t>
+          <t>Complementa a la MCIC</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>C-2025-46</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>México</t>
-        </is>
-      </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>Universidad Popular Autónoma del Estado de Puebla UPAEP</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
+          <t>IMT Ataltique</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
           <t>Convenio Específico</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Convenio Específico de Movilidad Académica de Estudiantes y Docentes Objeto: El presente convenio tiene por objeto establecer las bases para la movilidad académica de estudiantes (pregrado y postgrado) de la facultad de ingeniería y de personal docente de la facultad de ingeniería de la “UDFJC” y de “UPAEP, A.C.”, en desarrollo del Convenio Marco de Cooperación celebrado entre “UPAEP, A.C.” y la “</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>C-2023-19</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Nacional</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>Colombia IES</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Fundación UNIR</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr">
-        <is>
-          <t>Convenio Específico</t>
-        </is>
-      </c>
-      <c r="F10" s="14" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="inlineStr">
-        <is>
-          <t>El objeto de este convenio consiste en regular la cooperación entre la UDFJC y la FUNDACIÓN para permitir el desarrollo del programa académico conjunto “Pregrado en Ingeniería de Software”, que se impartirá en modalidad virtual, previa obtención por la UDFJC del registro calificado adscrito a la Facultad de Ingeniería otorgado por el Ministerio de Educación Nacional (MEN), bajo los mecanismos y es</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>C-2025-46</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Internacional</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>IMT Ataltique</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>Convenio Específico</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>Vigente</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
+          <t>Cadena de Formación</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>2030-11-21 (Vigente)</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>El objeto de este acuerdo es establecer los términos y condiciones bajo los cuales los estudiantes de pregrado de la Facultad de Ingeniería de la UDFJC tendrán acceso a los programas de estudios de posgrado del IMT Atlantique en el marco de la estrategia de cadena de formación para el doble diploma.</t>
         </is>
       </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I9"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C17"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="4" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Convenio específico de cooperación N.° 5570 de 2025 — Instituto Geográfico Agustín Codazzi (IGAC) y Universidad Distrital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Aunar esfuerzos académicos y administrativos para un programa de fortalecimiento en geografía, geomática, catastro, inteligencia artificial y ciencia de datos, mediante proyectos de maestría y doctorado. Nació de las conversaciones del IGAC con la coordinación de la MCIC; supervisa por la UD la Oficina de Investigaciones con apoyo de docentes de la Maestría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Detalle</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Vigencia</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>24 meses desde el acta de inicio del 11 de noviembre de 2025 (hasta el 7 de noviembre de 2027); estado: en ejecución (SECOP II)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Aportes</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>IGAC $50.000.000 en dinero; Universidad Distrital $36.480.000 en especie (total $86.480.000)</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Marco</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Convenio marco IGAC-UDFJC C-2023-1 (cooperación en investigación y programas de formación)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>Soporte (carpeta Anexos)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr"/>
+      <c r="C11" s="13" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Acta de la mesa técnica del 3 de junio de 2026 (apoyo a la supervisión).pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Convenio específico de cooperación 5570 de 2025 (IGAC - UDFJC).pdf</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n"/>
+      <c r="C13" s="14" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Designación del comité técnico por el IGAC (septiembre de 2026).pdf</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Designación del representante de la UD ante el comité técnico (agosto de 2026).pdf</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n"/>
+      <c r="C15" s="14" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Designación de apoyo a la supervisión (marzo de 2026).pdf</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>SECOP II - Convenio específico 5570 de 2025.pdf</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n"/>
+      <c r="C17" s="14" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL/a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 7. INTERACCIÓN CON EL ENTORNO NACIONAL E INTERNACIONAL/a. Diagnostico de convenios vigentes/F7_Convenios_URELINTER_Profundizacion.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Convenio IGAC" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Convenios vigentes'!$A$4:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Convenios vigentes'!$A$4:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -716,7 +716,7 @@
         <v>167</v>
       </c>
       <c r="G13" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
@@ -875,7 +875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>C-2019-28</t>
+          <t>CE-5570-2025</t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Nacional</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Colombia Otros Organismos</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Universidad de Valparaiso</t>
+          <t>Instituto Geográfico Agustín Codazzi - IGAC</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -1030,17 +1030,17 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>Movilidad de estudiantes</t>
+          <t>Cooperación (proyectos de maestría y doctorado)</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>2027-06-26 (Renovación Automática)</t>
+          <t>2027-11-07 (En ejecución)</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>Convenio de Intercambio y/o movilidad estudiantil Objeto: Establecer un programa de intercambio estudiantil, en el podrán participar todos los estudiantes de la UDFJC y los estudiantes de la Escuela de Ingeniería Civil Industrial de la Facultad de Ingeniería de la Universidad de Valparaíso, el cual será regulado en el presente convenio.</t>
+          <t>Convenio específico de cooperación N.° 5570 de 2025: aunar esfuerzos académicos y administrativos para un programa de fortalecimiento en geografía, geomática, catastro, inteligencia artificial y ciencia de datos, mediante proyectos de maestría y doctorado. Se origina en el trabajo del IGAC con la coordinación de la MCIC.</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>C-2022-29</t>
+          <t>C-2019-28</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Universidad Popular Autónoma del Estado de Puebla UPAEP</t>
+          <t>Universidad de Valparaiso</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -1077,44 +1077,44 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Movilidad estudianestes Facultad de Ingeniería</t>
+          <t>Movilidad de estudiantes</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>2027-08-17 (Vigente)</t>
+          <t>2027-06-26 (Renovación Automática)</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Convenio Específico de Movilidad Académica de Estudiantes y Docentes Objeto: El presente convenio tiene por objeto establecer las bases para la movilidad académica de estudiantes (pregrado y postgrado) de la facultad de ingeniería y de personal docente de la facultad de ingeniería de la “UDFJC” y de “UPAEP, A.C.”, en desarrollo del Convenio Marco de Cooperación celebrado entre “UPAEP, A.C.” y la “UDFJC”.</t>
+          <t>Convenio de Intercambio y/o movilidad estudiantil Objeto: Establecer un programa de intercambio estudiantil, en el podrán participar todos los estudiantes de la UDFJC y los estudiantes de la Escuela de Ingeniería Civil Industrial de la Facultad de Ingeniería de la Universidad de Valparaíso, el cual será regulado en el presente convenio.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Complementa a la MCIC</t>
+          <t>Aplica a la MCIC</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>C-2023-19</t>
+          <t>C-2022-29</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Nacional</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Colombia IES</t>
+          <t>México</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Fundación UNIR</t>
+          <t>Universidad Popular Autónoma del Estado de Puebla UPAEP</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -1124,17 +1124,17 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>Cotitulación</t>
+          <t>Movilidad estudianestes Facultad de Ingeniería</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>2030-06-28 (Vigente)</t>
+          <t>2027-08-17 (Vigente)</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>El objeto de este convenio consiste en regular la cooperación entre la UDFJC y la FUNDACIÓN para permitir el desarrollo del programa académico conjunto “Pregrado en Ingeniería de Software”, que se impartirá en modalidad virtual, previa obtención por la UDFJC del registro calificado adscrito a la Facultad de Ingeniería otorgado por el Ministerio de Educación Nacional (MEN), bajo los mecanismos y estrategias para el desarrollo conjunto de los procesos de diseño y gestión de las actividades académicas del programa que se desarrollan en el presente instrumento.</t>
+          <t>Convenio Específico de Movilidad Académica de Estudiantes y Docentes Objeto: El presente convenio tiene por objeto establecer las bases para la movilidad académica de estudiantes (pregrado y postgrado) de la facultad de ingeniería y de personal docente de la facultad de ingeniería de la “UDFJC” y de “UPAEP, A.C.”, en desarrollo del Convenio Marco de Cooperación celebrado entre “UPAEP, A.C.” y la “UDFJC”.</t>
         </is>
       </c>
     </row>
@@ -1146,47 +1146,94 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>C-2023-19</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Colombia IES</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Fundación UNIR</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Convenio Específico</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Cotitulación</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>2030-06-28 (Vigente)</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>El objeto de este convenio consiste en regular la cooperación entre la UDFJC y la FUNDACIÓN para permitir el desarrollo del programa académico conjunto “Pregrado en Ingeniería de Software”, que se impartirá en modalidad virtual, previa obtención por la UDFJC del registro calificado adscrito a la Facultad de Ingeniería otorgado por el Ministerio de Educación Nacional (MEN), bajo los mecanismos y estrategias para el desarrollo conjunto de los procesos de diseño y gestión de las actividades académicas del programa que se desarrollan en el presente instrumento.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>Complementa a la MCIC</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>C-2025-46</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Internacional</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Francia</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>IMT Ataltique</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>Convenio Específico</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>Cadena de Formación</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>2030-11-21 (Vigente)</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>El objeto de este acuerdo es establecer los términos y condiciones bajo los cuales los estudiantes de pregrado de la Facultad de Ingeniería de la UDFJC tendrán acceso a los programas de estudios de posgrado del IMT Atlantique en el marco de la estrategia de cadena de formación para el doble diploma.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I9"/>
+  <autoFilter ref="A4:I10"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
